--- a/rule_validation_report.xlsx
+++ b/rule_validation_report.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rule Validation" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rule Report" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -47,6 +47,11 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -60,17 +65,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -436,15 +440,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -454,316 +451,498 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>rule1</t>
+          <t>Rules Derived from Table</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>rule2</t>
+          <t>Comparison</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>flag</t>
+          <t>Score</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>score</t>
+          <t>Rules Derived from Document</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>BR1</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;b&gt;For Case 1, an individual is eligible for coverage if they are classified as an Employee and work 30 or more hours per week.&lt;/b&gt;&lt;br&gt;&lt;br&gt;
-&lt;table class="inner-table"&gt;
-&lt;tr&gt;&lt;th&gt;Employment Type&lt;/th&gt;&lt;th&gt;Working Hours&lt;/th&gt;&lt;th&gt;Condition 3 Field&lt;/th&gt;&lt;th&gt;Condition 3 Operator&lt;/th&gt;&lt;th&gt;Condition 3 Value&lt;/th&gt;&lt;th&gt;Action&lt;/th&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td&gt;Employee&lt;/td&gt;&lt;td&gt;30&lt;/td&gt;&lt;td&gt;nan&lt;/td&gt;&lt;td&gt;nan&lt;/td&gt;&lt;td&gt;nan&lt;/td&gt;&lt;td&gt;Eligible for Coverage&lt;/td&gt;&lt;/tr&gt;
-&lt;/table&gt;
-</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;b&gt;Eligibility for coverage based on employment classification and hours worked.&lt;/b&gt;&lt;br&gt;&lt;br&gt;
-&lt;table class="inner-table"&gt;
-&lt;tr&gt;&lt;th&gt;Employment Classification&lt;/th&gt;&lt;th&gt;Hours Worked per Week&lt;/th&gt;&lt;th&gt;Action&lt;/th&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td&gt;Employee&lt;/td&gt;&lt;td&gt;30&lt;/td&gt;&lt;td&gt;Eligible for coverage&lt;/td&gt;&lt;/tr&gt;
-&lt;/table&gt;
-</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Hours Worked Per Week</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Condition 3 Field</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Employment Type</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Employment Status</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Working Hours</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 30</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nan | </t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Employee | </t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | Employee</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30 | </t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ACTION: Eligible for Coverage | Eligible for coverage</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>BR2</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;b&gt;For Case 2, if an individual is unable to perform their duties at work, is under doctor care, and is currently not working, then they should be considered disabled.&lt;/b&gt;&lt;br&gt;&lt;br&gt;
-&lt;table class="inner-table"&gt;
-&lt;tr&gt;&lt;th&gt;Work Ability&lt;/th&gt;&lt;th&gt;Doctor Care&lt;/th&gt;&lt;th&gt;Currently Working&lt;/th&gt;&lt;th&gt;Action&lt;/th&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td&gt;Unable to perform duties&lt;/td&gt;&lt;td&gt;Yes&lt;/td&gt;&lt;td&gt;No&lt;/td&gt;&lt;td&gt;Considered Disabled&lt;/td&gt;&lt;/tr&gt;
-&lt;/table&gt;
-</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;b&gt;Validation rule for determining disability based on work capability, medical care, and employment status.&lt;/b&gt;&lt;br&gt;&lt;br&gt;
-&lt;table class="inner-table"&gt;
-&lt;tr&gt;&lt;th&gt;ability_to_perform_duties&lt;/th&gt;&lt;th&gt;doctor_care&lt;/th&gt;&lt;th&gt;employment_status&lt;/th&gt;&lt;th&gt;Action&lt;/th&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td&gt;unable&lt;/td&gt;&lt;td&gt;under care&lt;/td&gt;&lt;td&gt;not working&lt;/td&gt;&lt;td&gt;considered disabled&lt;/td&gt;&lt;/tr&gt;
-&lt;/table&gt;
-</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>employment_status</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Currently Working</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ability_to_perform_duties</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>doctor_care</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Doctor Care</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Work Ability</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | not working</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No | </t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | unable</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | under care</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes | </t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unable to perform duties | </t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ACTION: Considered Disabled | considered disabled</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>66.67%</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>BR3</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;b&gt;For Case 3, if the Elimination Period has been completed (indicated by a value of 'Yes'), then the action to take is to start the benefit payment.&lt;/b&gt;&lt;br&gt;&lt;br&gt;
-&lt;table class="inner-table"&gt;
-&lt;tr&gt;&lt;th&gt;Elimination Period Completed&lt;/th&gt;&lt;th&gt;Action&lt;/th&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td&gt;Yes&lt;/td&gt;&lt;td&gt;Start Benefit Payment&lt;/td&gt;&lt;/tr&gt;
-&lt;/table&gt;
-</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;b&gt;Rule to validate benefit payment initiation based on the completion of the Elimination Period.&lt;/b&gt;&lt;br&gt;&lt;br&gt;
-&lt;table class="inner-table"&gt;
-&lt;tr&gt;&lt;th&gt;Elimination Period Completed&lt;/th&gt;&lt;th&gt;Action&lt;/th&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td&gt;Yes&lt;/td&gt;&lt;td&gt;Start the benefit payment&lt;/td&gt;&lt;/tr&gt;
-&lt;/table&gt;
-</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Elimination Period Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Yes | Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ACTION: Start Benefit Payment | Start the benefit payment</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>BR4</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;b&gt;For Case 4, an individual is eligible for coverage if they are classified as an Employee and work fewer than 30 hours per week.&lt;/b&gt;&lt;br&gt;&lt;br&gt;
-&lt;table class="inner-table"&gt;
-&lt;tr&gt;&lt;th&gt;Employment Type&lt;/th&gt;&lt;th&gt;Working Hours&lt;/th&gt;&lt;th&gt;Action&lt;/th&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td&gt;Employee&lt;/td&gt;&lt;td&gt;30&lt;/td&gt;&lt;td&gt;Eligible for Coverage&lt;/td&gt;&lt;/tr&gt;
-&lt;/table&gt;
-</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;b&gt;Eligibility for coverage based on employment status and hours worked.&lt;/b&gt;&lt;br&gt;&lt;br&gt;
-&lt;table class="inner-table"&gt;
-&lt;tr&gt;&lt;th&gt;Employee Classification&lt;/th&gt;&lt;th&gt;Hours Worked per Week&lt;/th&gt;&lt;th&gt;Action&lt;/th&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td&gt;Employee&lt;/td&gt;&lt;td&gt;30&lt;/td&gt;&lt;td&gt;Eligible for coverage&lt;/td&gt;&lt;/tr&gt;
-&lt;/table&gt;
-</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Working Hours</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Employment Type</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Employee Classification</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Hours Worked per Week</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30 | </t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Employee | </t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | Employee</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ACTION: Eligible for Coverage | Eligible for coverage</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>BR5</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;b&gt;For Case 5, the individual is unable to perform their work duties and is currently not working. Based on these conditions, they are considered disabled.&lt;/b&gt;&lt;br&gt;&lt;br&gt;
-&lt;table class="inner-table"&gt;
-&lt;tr&gt;&lt;th&gt;Work Ability&lt;/th&gt;&lt;th&gt;Currently Working&lt;/th&gt;&lt;th&gt;Action&lt;/th&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td&gt;Unable to perform duties&lt;/td&gt;&lt;td&gt;No&lt;/td&gt;&lt;td&gt;Considered Disabled&lt;/td&gt;&lt;/tr&gt;
-&lt;/table&gt;
-</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;b&gt;Validation rule for determining disability status based on work duties and current employment status.&lt;/b&gt;&lt;br&gt;&lt;br&gt;
-&lt;table class="inner-table"&gt;
-&lt;tr&gt;&lt;th&gt;work_duties_performance&lt;/th&gt;&lt;th&gt;current_employment_status&lt;/th&gt;&lt;th&gt;Action&lt;/th&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td&gt;true&lt;/td&gt;&lt;td&gt;true&lt;/td&gt;&lt;td&gt;considered_disabled&lt;/td&gt;&lt;/tr&gt;
-&lt;/table&gt;
-</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Work Ability</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Currently Working</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>current_work_status</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>work_duties_performance</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unable to perform duties | </t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No | </t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | not working</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | unable</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ACTION: Considered Disabled | considered disabled</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>BR6</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;b&gt;For Case 6, if the elimination period has not been completed, then the benefit payment should be started.&lt;/b&gt;&lt;br&gt;&lt;br&gt;
-&lt;table class="inner-table"&gt;
-&lt;tr&gt;&lt;th&gt;Elimination Period Completed&lt;/th&gt;&lt;th&gt;Action&lt;/th&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td&gt;No&lt;/td&gt;&lt;td&gt;Start Benefit Payment&lt;/td&gt;&lt;/tr&gt;
-&lt;/table&gt;
-</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;b&gt;Validation rule for benefit payment initiation based on the elimination period completion.&lt;/b&gt;&lt;br&gt;&lt;br&gt;
-&lt;table class="inner-table"&gt;
-&lt;tr&gt;&lt;th&gt;elimination_period_completed&lt;/th&gt;&lt;th&gt;Action&lt;/th&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td&gt;false&lt;/td&gt;&lt;td&gt;start_benefit_payment&lt;/td&gt;&lt;/tr&gt;
-&lt;/table&gt;
-</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Elimination Period Completed</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Elimination Period Completion</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No | </t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | true</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ACTION: Start Benefit Payment | start the benefit payment</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>BR7</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100 | </t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ACTION: Coverage Continues | coverage will continue</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>BR7</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;b&gt;For Case 7, if the individual's age is greater than 100 years, then the action taken will be that coverage continues.&lt;/b&gt;&lt;br&gt;&lt;br&gt;
-&lt;table class="inner-table"&gt;
-&lt;tr&gt;&lt;th&gt;Age&lt;/th&gt;&lt;th&gt;Condition 2 Field&lt;/th&gt;&lt;th&gt;Condition 3 Field&lt;/th&gt;&lt;th&gt;Action&lt;/th&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td&gt;100&lt;/td&gt;&lt;td&gt;Condition 2 Value&lt;/td&gt;&lt;td&gt;Condition 3 Value&lt;/td&gt;&lt;td&gt;Coverage Continues&lt;/td&gt;&lt;/tr&gt;
-&lt;/table&gt;
-</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;b&gt;For Case 7, if the individual's age is greater than 100 years, then the action taken will be that coverage continues.&lt;/b&gt;&lt;br&gt;&lt;br&gt;
-&lt;table class="inner-table"&gt;
-&lt;tr&gt;&lt;th&gt;age&lt;/th&gt;&lt;th&gt;Action&lt;/th&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td&gt;100&lt;/td&gt;&lt;td&gt;coverage continues&lt;/td&gt;&lt;/tr&gt;
-&lt;/table&gt;
-</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>BR8</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>employment_status</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Currently Working</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | currently working</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes | </t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ACTION: Considered Disabled | considered disabled</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>33.33%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>BR8</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;b&gt;For Case 8, if the individual is currently working and has confirmed that they are employed, then they should be considered disabled.&lt;/b&gt;&lt;br&gt;&lt;br&gt;
-&lt;table class="inner-table"&gt;
-&lt;tr&gt;&lt;th&gt;Currently Working&lt;/th&gt;&lt;th&gt;Action&lt;/th&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td&gt;Yes&lt;/td&gt;&lt;td&gt;Considered Disabled&lt;/td&gt;&lt;/tr&gt;
-&lt;/table&gt;
-</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;b&gt;For Case 8, if the individual is currently working and has confirmed that they are employed, then they should be considered disabled.&lt;/b&gt;&lt;br&gt;&lt;br&gt;
-&lt;table class="inner-table"&gt;
-&lt;tr&gt;&lt;th&gt;employment_status&lt;/th&gt;&lt;th&gt;employment_confirmation&lt;/th&gt;&lt;th&gt;Action&lt;/th&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td&gt;currently working&lt;/td&gt;&lt;td&gt;confirmed&lt;/td&gt;&lt;td&gt;considered disabled&lt;/td&gt;&lt;/tr&gt;
-&lt;/table&gt;
-</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
